--- a/用卷/1991,1992.xlsx
+++ b/用卷/1991,1992.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDBAF6D-4772-485D-8190-D6AB3BC01988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292D0C5C-B049-4D27-84AF-83D974467499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="56">
   <si>
     <t>年份</t>
   </si>
@@ -205,6 +205,10 @@
   </si>
   <si>
     <t>分科卷数统计</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国卷,三南卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1148,10 +1152,10 @@
         <v>33</v>
       </c>
       <c r="B41" s="4">
-        <v>3</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="D41" s="7"/>
     </row>
@@ -1184,10 +1188,10 @@
         <v>36</v>
       </c>
       <c r="B44" s="4">
-        <v>3</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="D44" s="7"/>
     </row>
